--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>116713245</v>
       </c>
       <c r="B10" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>116713245</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>116713245</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -1544,11 +1544,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>116713245</v>
       </c>
       <c r="B10" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>116713245</v>
       </c>
       <c r="B10" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>116713245</v>
       </c>
       <c r="B10" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>116713245</v>
       </c>
       <c r="B10" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
